--- a/produkty_cenotvorba.xlsx
+++ b/produkty_cenotvorba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdvor\Desktop\poolzone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE87621-E264-4F36-BFB2-500E8FC40CF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFF8EE87-8E6E-42D7-9771-3432D3D00DF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="1670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="1833">
   <si>
     <t>Skupina</t>
   </si>
@@ -5038,17 +5038,514 @@
   </si>
   <si>
     <t>Dávkovací čerpadlo komplet vč. hadičky a sacího koše Mr.Pure (V1.2)</t>
+  </si>
+  <si>
+    <t>Samostatná úprava cen  u různých produktů</t>
+  </si>
+  <si>
+    <t>Čerpadlo Badu Picco II/5 5m3/hod 230V</t>
+  </si>
+  <si>
+    <t>Čerpadlo Badu Magic II/4 4 m3/hod 230V 0,35/0,18 kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo Badu Magic II/6 6 m3/hod 230V 0,45/0,25 kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo Badu Magic II/8 8 m3/hod 230V 0,61/0,40 kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo Badu Magic II/11 11 m3/hod 230V 0,72/0,45 kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo BADU TOP II/8 8 m3/hod 230V 0,57/0,30 kW (Bettar)</t>
+  </si>
+  <si>
+    <t>Čerpadlo BADU TOP II/12 12 m3/hod 230V 0,72/0,45 kW (Bettar)</t>
+  </si>
+  <si>
+    <t>Čerpadlo BADU TOP II/14 14 m3/hod 230V 0,97/0,65 kW (Bettar)</t>
+  </si>
+  <si>
+    <t>297.0075.402</t>
+  </si>
+  <si>
+    <t>297.0150.402</t>
+  </si>
+  <si>
+    <t>297.0220.402</t>
+  </si>
+  <si>
+    <t>297.0400.402</t>
+  </si>
+  <si>
+    <t>297.0550.402</t>
+  </si>
+  <si>
+    <t>210.2321.138</t>
+  </si>
+  <si>
+    <t>Badu PRIME 7, 7m3/h 230V 0,5kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 11, 11m3/h 230V 0,69kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 13, 13m3/h 230V 0,85kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 15, 15 m3/h 230V 1,10kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 20, 20m3/h 230V 1,40kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 25, 25 m3/h 230V 1,85kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 30, 30m3/h 230V 2,00kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 40, 40m3/h 230V 2,90kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 48, 48m3/h 230V 3,45kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 7, 7m3/h 400V 0,5kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 11, 11m3/h 400V 0,69kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 13, 13m3/h 400V 0,85kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 15, 15 m3/h 400V 1,10kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 20, 20m3/h 400V 1,40kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 25, 25m3/h 400V 1,62kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 30, 30m3/h 400V 1,85kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 40, 40m3/h 400V 2,64kW</t>
+  </si>
+  <si>
+    <t>Badu PRIME 48, 48m3/h 400V 3,10kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 30 30m3/h 400V 1,85kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 40, 40m3/h 400V 2,64kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 45, 45m3/h 400V 3,10kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 50, 50m3/h 400V 3,45kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 55, 55m3/h 400/690V 4,66kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 60, 60m3/h 400V 3,10kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 70, 70m3/h 400V 3,55kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 80, 80m3/h 400/690V 4,66kW</t>
+  </si>
+  <si>
+    <t>Badu RESORT 110, 110m3/h 400/690V 6,35kW</t>
+  </si>
+  <si>
+    <t>Badu ECO DRIVE II 0,75kW 380-480V</t>
+  </si>
+  <si>
+    <t>Badu ECO DRIVE II 1,5kW 380-480V</t>
+  </si>
+  <si>
+    <t>Badu ECO DRIVE II 2,2kW 380-480V</t>
+  </si>
+  <si>
+    <t>Badu ECO DRIVE II 4,0kW 380-480V</t>
+  </si>
+  <si>
+    <t>Badu ECO DRIVE II 5,5kW 380-480V</t>
+  </si>
+  <si>
+    <t>Čerpadlo BADU Profi Eco VS, 230V 1,4kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo Badu Magna 8, 8m3/h 230V</t>
+  </si>
+  <si>
+    <t>Čerpadlo Badu Magna 12, 12 m3/h 230V</t>
+  </si>
+  <si>
+    <t>Čerpadlo Badu Magna 14, 14 m3/h 230V</t>
+  </si>
+  <si>
+    <t>460144T</t>
+  </si>
+  <si>
+    <t>460145T</t>
+  </si>
+  <si>
+    <t>460143T</t>
+  </si>
+  <si>
+    <t>460142T</t>
+  </si>
+  <si>
+    <t>460141T</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA NIPER 400M 6m3/hod</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 200 31T 29 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 300 36T 33 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA NOX 20 4M (Basic)</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA NOX 25 6M (Niper)</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA NOX 33 8M (Iris 500)</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA NOX 50 12M (Iris 750)</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA NOX 100 15M (Iris 1000)</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen I 33 8M (Iris 500)</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen I 50 12M (Iris 750)</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen I 100 15M (Iris 1000)</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S 60M 12m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S 75M 14 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S 100 18M 17 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S 150 22M 21 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 75 15M 15 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 100 24M 21 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 150 29M 25 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 200 31M 29 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 300 36M 33 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 150 29T 25 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 100 24T 21m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA Silen S2 75 15T 15 m3/h</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA NOX 100 18M, 18m3/h 230V</t>
+  </si>
+  <si>
+    <t>Čerpadlo ESPA NOX 150 22M, 22 m3/h 230V</t>
+  </si>
+  <si>
+    <t>Čerpadlo SS033 (náhrada FXP 250) 5 m3/h 230V 0,43kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo SS075 (náhrada FXP 550) 12 m3/h 230V 0,75kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo SS100 (náhrada FXP 750) 14 m3/h 230V 0,90kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo PREVA 75 12 m3/h 230V 0,80kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo PREVA 50 9 m3/h 230V 0,57kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo PREVA 33 6 m3/h 230V 0,38kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo PREVA 100 16 m3/h 230V 1,06kW</t>
+  </si>
+  <si>
+    <t>Čerpadlo PREVA 25 4 m3/h 230V 0,29kW</t>
+  </si>
+  <si>
+    <t>SMC10</t>
+  </si>
+  <si>
+    <t>SMC15</t>
+  </si>
+  <si>
+    <t>SMC20</t>
+  </si>
+  <si>
+    <t>85D1220</t>
+  </si>
+  <si>
+    <t>85D1221</t>
+  </si>
+  <si>
+    <t>85D1222</t>
+  </si>
+  <si>
+    <t>85D1236</t>
+  </si>
+  <si>
+    <t>85D1237</t>
+  </si>
+  <si>
+    <t>85D1238</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Zelia ZLT 25 do 25 m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Zelia ZLT 50 do 50 m3</t>
+  </si>
+  <si>
+    <t>Minisalt NPS 4/20 do 15m3</t>
+  </si>
+  <si>
+    <t>Minisalt NPS 8/40 do 30m3</t>
+  </si>
+  <si>
+    <t>Minisalt NPS 12/60 do 60m3</t>
+  </si>
+  <si>
+    <t>Minisalt NPS 16/80 do 80m3</t>
+  </si>
+  <si>
+    <t>Minisalt NPS 23/120 do 100m3</t>
+  </si>
+  <si>
+    <t>Minisalt NPS 30/160 do 160m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 10   do 30m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 15   do 50m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 20   do 80m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 10 pHW s dávkováním pH do 25m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 15 pHW s dávkováním pH do 50m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 20 pHW s dávkováním pH do 80m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 10 ORP sonda + pHW s dávkováním pH do 25m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 15 ORP sonda + pHW s dávkováním pH do 50m3</t>
+  </si>
+  <si>
+    <t>Solonizační jednotka Innowater SMC 20 ORP sonda + pHW s dávkováním pH do 80m3</t>
+  </si>
+  <si>
+    <t>CELM12TRA04P</t>
+  </si>
+  <si>
+    <t>CELM12TRA03P</t>
+  </si>
+  <si>
+    <t>CELM12TRA06P</t>
+  </si>
+  <si>
+    <t>CEGE13PACS055</t>
+  </si>
+  <si>
+    <t>AK12202</t>
+  </si>
+  <si>
+    <t>DES13CE</t>
+  </si>
+  <si>
+    <t>AK12162</t>
+  </si>
+  <si>
+    <t>DESILC13REP</t>
+  </si>
+  <si>
+    <t>CEGE09MONESR200</t>
+  </si>
+  <si>
+    <t>PF160100</t>
+  </si>
+  <si>
+    <t>PF160102</t>
+  </si>
+  <si>
+    <t>CEGE13PACS095</t>
+  </si>
+  <si>
+    <t>85SMC10</t>
+  </si>
+  <si>
+    <t>85SMC15</t>
+  </si>
+  <si>
+    <t>85SMC20</t>
+  </si>
+  <si>
+    <t>CEGE13PACS040</t>
+  </si>
+  <si>
+    <t>CELM12TRA09P</t>
+  </si>
+  <si>
+    <t>CELM12TRA07P</t>
+  </si>
+  <si>
+    <t>DES2C15REP</t>
+  </si>
+  <si>
+    <t>CELM12TRA02P</t>
+  </si>
+  <si>
+    <t>CELM12TRA05P</t>
+  </si>
+  <si>
+    <t>Náhradní článek - cela EcoMatik ESC 24/36/40</t>
+  </si>
+  <si>
+    <t>Náhradní článek - cela EcoMatik ESC 16</t>
+  </si>
+  <si>
+    <t>Náhradní článek - cela EcoMatik BMSC 20</t>
+  </si>
+  <si>
+    <t>Náhradní článek - cela EcoMatik BMSC 13</t>
+  </si>
+  <si>
+    <t>Náhradní článek - cela EcoMatik BMSC 26</t>
+  </si>
+  <si>
+    <t>Náhradní článek - cela EcoMatik BMSC 8</t>
+  </si>
+  <si>
+    <t>Cela 4P (Minisalt 50, NPS 12/60)</t>
+  </si>
+  <si>
+    <t>Cela 3P (Poolsquad 35, NPS 8/40)</t>
+  </si>
+  <si>
+    <t>Cela 6P (NPS 23/120, JS 120, PSQ 95)</t>
+  </si>
+  <si>
+    <t>Cela Pacific 55 - 7 plechů</t>
+  </si>
+  <si>
+    <t>Cela Asin Aqua Salt TE-25</t>
+  </si>
+  <si>
+    <t>Náhradní článek k BMSC13 inline (nový typ)</t>
+  </si>
+  <si>
+    <t>Náhradní elektroda TE-25 bez těla a uzávěru ASEKO</t>
+  </si>
+  <si>
+    <t>Náhradní cela EcoSalt 13 InLine cell</t>
+  </si>
+  <si>
+    <t>Cela ESR 160/200 Pooltechnologie</t>
+  </si>
+  <si>
+    <t>Náhradní cela Zelia ZLT25</t>
+  </si>
+  <si>
+    <t>Náhradní cela Zelia ZLT50</t>
+  </si>
+  <si>
+    <t>Cela Pacific 95 - 7 plechů</t>
+  </si>
+  <si>
+    <t>Náhradní cela SMC 10</t>
+  </si>
+  <si>
+    <t>Náhradní cela SMC 15</t>
+  </si>
+  <si>
+    <t>Náhradní cela SMC 20</t>
+  </si>
+  <si>
+    <t>Cela Pacific 40 - 9P 85mm</t>
+  </si>
+  <si>
+    <t>Cela 9P</t>
+  </si>
+  <si>
+    <t>Cela 7P (NPS 30/160)</t>
+  </si>
+  <si>
+    <t>Náhradní cela EcoSalt2 15g</t>
+  </si>
+  <si>
+    <t>Cela 2P (Minisalt 30, NPS 4/20)</t>
+  </si>
+  <si>
+    <t>Cela 5P (Minisalt 70, NPS 16/80, PSQ 55)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5088,6 +5585,32 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -5137,68 +5660,81 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hypertextový odkaz" xfId="1" builtinId="8"/>
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -5421,10 +5957,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1067"/>
+  <dimension ref="A1:G1170"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="1" max="1" width="40.140625" customWidth="1"/>
     <col min="2" max="2" width="43.7109375" customWidth="1"/>
     <col min="3" max="4" width="35.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
@@ -20140,7 +20676,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="1041" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1041" s="27" t="s">
         <v>1666</v>
       </c>
@@ -20154,7 +20690,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="1042" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1042" s="27" t="s">
         <v>1667</v>
       </c>
@@ -20168,7 +20704,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="1043" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1043" s="27" t="s">
         <v>1668</v>
       </c>
@@ -20182,7 +20718,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="1044" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1044" s="27" t="s">
         <v>1669</v>
       </c>
@@ -20196,128 +20732,1383 @@
         <v>160</v>
       </c>
     </row>
-    <row r="1045" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1045" s="18"/>
       <c r="D1045" s="24"/>
       <c r="G1045" s="29"/>
     </row>
-    <row r="1046" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1046" s="18"/>
       <c r="D1046" s="23"/>
       <c r="G1046" s="29"/>
     </row>
-    <row r="1047" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1047" s="18"/>
       <c r="D1047" s="24"/>
       <c r="G1047" s="29"/>
     </row>
-    <row r="1048" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1048" t="s">
+        <v>1670</v>
+      </c>
       <c r="B1048" s="18"/>
       <c r="D1048" s="23"/>
       <c r="G1048" s="29"/>
     </row>
-    <row r="1049" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1049" s="18"/>
       <c r="D1049" s="24"/>
       <c r="G1049" s="29"/>
     </row>
-    <row r="1050" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1050" s="18"/>
-      <c r="D1050" s="23"/>
-      <c r="G1050" s="29"/>
-    </row>
-    <row r="1051" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1051" s="18"/>
-      <c r="D1051" s="24"/>
-      <c r="G1051" s="29"/>
-    </row>
-    <row r="1052" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1052" s="18"/>
-      <c r="D1052" s="23"/>
-      <c r="G1052" s="29"/>
-    </row>
-    <row r="1053" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1053" s="18"/>
-      <c r="D1053" s="24"/>
-      <c r="G1053" s="29"/>
-    </row>
-    <row r="1054" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1054" s="18"/>
-      <c r="D1054" s="23"/>
-      <c r="G1054" s="29"/>
-    </row>
-    <row r="1055" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1055" s="18"/>
-      <c r="D1055" s="24"/>
-      <c r="G1055" s="29"/>
-    </row>
-    <row r="1056" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1056" s="18"/>
-      <c r="D1056" s="23"/>
-      <c r="G1056" s="29"/>
+    <row r="1050" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1050" s="27" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D1050" s="27">
+        <v>410005</v>
+      </c>
+      <c r="G1050" s="31">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1051" s="30"/>
+      <c r="B1051" s="27" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D1051" s="27">
+        <v>410004</v>
+      </c>
+      <c r="G1051" s="31">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1052" s="27" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D1052" s="27">
+        <v>410006</v>
+      </c>
+      <c r="G1052" s="31">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1053" s="27" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D1053" s="27">
+        <v>410008</v>
+      </c>
+      <c r="G1053" s="31">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1054" s="27" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D1054" s="27">
+        <v>410011</v>
+      </c>
+      <c r="G1054" s="31">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1055" s="27" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D1055" s="27">
+        <v>420008</v>
+      </c>
+      <c r="G1055" s="31">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1056" s="27" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D1056" s="27">
+        <v>420012</v>
+      </c>
+      <c r="G1056" s="31">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="1057" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1057" s="18"/>
-      <c r="D1057" s="24"/>
-      <c r="G1057" s="29"/>
+      <c r="B1057" s="27" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D1057" s="27">
+        <v>420014</v>
+      </c>
+      <c r="G1057" s="31">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="1058" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1058" s="18"/>
-      <c r="D1058" s="23"/>
-      <c r="G1058" s="29"/>
+      <c r="B1058" s="27" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D1058" s="27">
+        <v>2190078038</v>
+      </c>
+      <c r="G1058" s="31">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="1059" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1059" s="18"/>
-      <c r="D1059" s="24"/>
-      <c r="G1059" s="29"/>
+      <c r="B1059" s="27" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D1059" s="27">
+        <v>2190118038</v>
+      </c>
+      <c r="G1059" s="31">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="1060" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1060" s="18"/>
-      <c r="D1060" s="23"/>
-      <c r="G1060" s="29"/>
+      <c r="B1060" s="27" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D1060" s="27">
+        <v>2190138038</v>
+      </c>
+      <c r="G1060" s="31">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="1061" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1061" s="18"/>
-      <c r="D1061" s="24"/>
-      <c r="G1061" s="3"/>
+      <c r="B1061" s="27" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D1061" s="27">
+        <v>2190158038</v>
+      </c>
+      <c r="G1061" s="31">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="1062" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1062" s="18"/>
-      <c r="D1062" s="23"/>
-      <c r="G1062" s="3"/>
+      <c r="B1062" s="27" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D1062" s="27">
+        <v>2190208038</v>
+      </c>
+      <c r="G1062" s="31">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="1063" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1063" s="18"/>
-      <c r="D1063" s="24"/>
-      <c r="G1063" s="3"/>
+      <c r="B1063" s="27" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D1063" s="27">
+        <v>2190258038</v>
+      </c>
+      <c r="G1063" s="31">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="1064" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1064" s="18"/>
-      <c r="D1064" s="23"/>
-      <c r="G1064" s="3"/>
+      <c r="B1064" s="27" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D1064" s="27">
+        <v>2190308038</v>
+      </c>
+      <c r="G1064" s="31">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="1065" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1065" s="18"/>
-      <c r="D1065" s="24"/>
-      <c r="G1065" s="3"/>
+      <c r="B1065" s="27" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D1065" s="27">
+        <v>2190408038</v>
+      </c>
+      <c r="G1065" s="31">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="1066" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1066" s="18"/>
-      <c r="D1066" s="23"/>
-      <c r="G1066" s="3"/>
+      <c r="B1066" s="27" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D1066" s="27">
+        <v>2190488038</v>
+      </c>
+      <c r="G1066" s="31">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="1067" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1067" s="18"/>
-      <c r="D1067" s="24"/>
-      <c r="G1067" s="3"/>
+      <c r="B1067" s="27" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D1067" s="27">
+        <v>2190078037</v>
+      </c>
+      <c r="G1067" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1068" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1068" s="27" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D1068" s="27">
+        <v>2190118037</v>
+      </c>
+      <c r="G1068" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1069" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1069" s="27" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D1069" s="27">
+        <v>2190138037</v>
+      </c>
+      <c r="G1069" s="31">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="1070" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1070" s="27" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D1070" s="27">
+        <v>2190158037</v>
+      </c>
+      <c r="G1070" s="31">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="1071" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1071" s="27" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D1071" s="27">
+        <v>2190208037</v>
+      </c>
+      <c r="G1071" s="31">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="1072" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1072" s="27" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D1072" s="27">
+        <v>2190258037</v>
+      </c>
+      <c r="G1072" s="31">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="1073" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1073" s="27" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D1073" s="27">
+        <v>2190308037</v>
+      </c>
+      <c r="G1073" s="31">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="1074" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1074" s="27" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D1074" s="27">
+        <v>2190408037</v>
+      </c>
+      <c r="G1074" s="31">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="1075" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1075" s="27" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D1075" s="27">
+        <v>2190488037</v>
+      </c>
+      <c r="G1075" s="31">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="1076" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1076" s="27" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D1076" s="27">
+        <v>2195308037</v>
+      </c>
+      <c r="G1076" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1077" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1077" s="27" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D1077" s="27">
+        <v>2195408037</v>
+      </c>
+      <c r="G1077" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1078" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1078" s="27" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D1078" s="27">
+        <v>2195458037</v>
+      </c>
+      <c r="G1078" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1079" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1079" s="27" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D1079" s="27">
+        <v>2195508037</v>
+      </c>
+      <c r="G1079" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1080" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1080" s="27" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D1080" s="27">
+        <v>2195558037</v>
+      </c>
+      <c r="G1080" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1081" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1081" s="27" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D1081" s="27">
+        <v>2195608037</v>
+      </c>
+      <c r="G1081" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1082" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1082" s="27" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D1082" s="27">
+        <v>2195708037</v>
+      </c>
+      <c r="G1082" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1083" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1083" s="27" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D1083" s="27">
+        <v>2195808037</v>
+      </c>
+      <c r="G1083" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1084" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1084" s="27" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D1084" s="27">
+        <v>2195118037</v>
+      </c>
+      <c r="G1084" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1085" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1085" s="27" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D1085" s="27" t="s">
+        <v>1679</v>
+      </c>
+      <c r="G1085" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1086" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1086" s="27" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D1086" s="27" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G1086" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1087" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1087" s="27" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D1087" s="27" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1087" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1088" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1088" s="27" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D1088" s="27" t="s">
+        <v>1682</v>
+      </c>
+      <c r="G1088" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1089" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1089" s="27" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D1089" s="27" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G1089" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1090" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1090" s="27" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D1090" s="27" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G1090" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1091" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1091" s="27" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D1091" s="27">
+        <v>2190088038</v>
+      </c>
+      <c r="G1091" s="31">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1092" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1092" s="27" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D1092" s="27">
+        <v>2190128038</v>
+      </c>
+      <c r="G1092" s="31">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1093" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1093" s="27" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D1093" s="27">
+        <v>2190148038</v>
+      </c>
+      <c r="G1093" s="31">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1094" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1094" s="27" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D1094" s="27">
+        <v>460111</v>
+      </c>
+      <c r="G1094" s="32">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1095" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1095" s="27" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D1095" s="27" t="s">
+        <v>1721</v>
+      </c>
+      <c r="G1095" s="32">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="1096" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1096" s="27" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D1096" s="27" t="s">
+        <v>1722</v>
+      </c>
+      <c r="G1096" s="32">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="1097" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1097" s="27" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D1097" s="27">
+        <v>461020</v>
+      </c>
+      <c r="G1097" s="32">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="1098" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1098" s="27" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D1098" s="27">
+        <v>461025</v>
+      </c>
+      <c r="G1098" s="32">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="1099" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1099" s="27" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D1099" s="27">
+        <v>461033</v>
+      </c>
+      <c r="G1099" s="32">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="1100" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1100" s="27" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D1100" s="27">
+        <v>461050</v>
+      </c>
+      <c r="G1100" s="32">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1101" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1101" s="27" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D1101" s="27">
+        <v>461100</v>
+      </c>
+      <c r="G1101" s="32">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1102" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1102" s="27" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D1102" s="27">
+        <v>460121</v>
+      </c>
+      <c r="G1102" s="32">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1103" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1103" s="27" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D1103" s="27">
+        <v>460122</v>
+      </c>
+      <c r="G1103" s="32">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1104" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1104" s="27" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D1104" s="27">
+        <v>460123</v>
+      </c>
+      <c r="G1104" s="32">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1105" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1105" s="27" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D1105" s="27">
+        <v>460131</v>
+      </c>
+      <c r="G1105" s="32">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1106" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1106" s="27" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D1106" s="27">
+        <v>460132</v>
+      </c>
+      <c r="G1106" s="32">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1107" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1107" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D1107" s="27">
+        <v>460133</v>
+      </c>
+      <c r="G1107" s="32">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1108" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1108" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D1108" s="27">
+        <v>460134</v>
+      </c>
+      <c r="G1108" s="32">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1109" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1109" s="27" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D1109" s="27">
+        <v>460141</v>
+      </c>
+      <c r="G1109" s="32">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1110" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1110" s="27" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D1110" s="27">
+        <v>460142</v>
+      </c>
+      <c r="G1110" s="32">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1111" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1111" s="27" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D1111" s="27">
+        <v>460143</v>
+      </c>
+      <c r="G1111" s="32">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1112" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1112" s="27" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D1112" s="27">
+        <v>460144</v>
+      </c>
+      <c r="G1112" s="32">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1113" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1113" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D1113" s="27">
+        <v>460145</v>
+      </c>
+      <c r="G1113" s="32">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1114" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1114" s="27" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D1114" s="27" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G1114" s="32">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1115" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1115" s="27" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D1115" s="27" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G1115" s="32">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1116" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1116" s="27" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D1116" s="27" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1116" s="32">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1117" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1117" s="27" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D1117" s="27">
+        <v>460108</v>
+      </c>
+      <c r="G1117" s="32">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1118" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1118" s="27" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D1118" s="27">
+        <v>460150</v>
+      </c>
+      <c r="G1118" s="32">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1119" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1119" s="27" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D1119" s="27">
+        <v>6171</v>
+      </c>
+      <c r="G1119" s="33">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="1120" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1120" s="27" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D1120" s="27">
+        <v>6378</v>
+      </c>
+      <c r="G1120" s="34">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="1121" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1121" s="27" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D1121" s="27">
+        <v>88022405</v>
+      </c>
+      <c r="G1121" s="33">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="1122" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1122" s="27" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D1122" s="27">
+        <v>573075</v>
+      </c>
+      <c r="G1122" s="32">
+        <v>0.85499999999999998</v>
+      </c>
+    </row>
+    <row r="1123" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1123" s="27" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D1123" s="27">
+        <v>573050</v>
+      </c>
+      <c r="G1123" s="32">
+        <v>0.85599999999999998</v>
+      </c>
+    </row>
+    <row r="1124" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1124" s="27" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D1124" s="27">
+        <v>573033</v>
+      </c>
+      <c r="G1124" s="32">
+        <v>0.90700000000000003</v>
+      </c>
+    </row>
+    <row r="1125" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1125" s="27" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D1125" s="27">
+        <v>573100</v>
+      </c>
+      <c r="G1125" s="32">
+        <v>0.85599999999999998</v>
+      </c>
+    </row>
+    <row r="1126" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1126" s="27" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D1126" s="27">
+        <v>573025</v>
+      </c>
+      <c r="G1126" s="32">
+        <v>0.85699999999999998</v>
+      </c>
+    </row>
+    <row r="1127" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1127" s="27" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D1127" s="27">
+        <v>950610</v>
+      </c>
+      <c r="G1127">
+        <v>0.70299999999999996</v>
+      </c>
+    </row>
+    <row r="1128" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1128" s="27" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D1128" s="27">
+        <v>950611</v>
+      </c>
+      <c r="G1128">
+        <v>0.74099999999999999</v>
+      </c>
+    </row>
+    <row r="1129" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1129" s="27" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D1129" s="27">
+        <v>852610</v>
+      </c>
+      <c r="G1129">
+        <v>0.68500000000000005</v>
+      </c>
+    </row>
+    <row r="1130" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1130" s="27" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D1130" s="27">
+        <v>852611</v>
+      </c>
+      <c r="G1130">
+        <v>0.64200000000000002</v>
+      </c>
+    </row>
+    <row r="1131" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1131" s="27" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D1131" s="27">
+        <v>852612</v>
+      </c>
+      <c r="G1131">
+        <v>0.66800000000000004</v>
+      </c>
+    </row>
+    <row r="1132" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1132" s="27" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D1132" s="27">
+        <v>852613</v>
+      </c>
+      <c r="G1132">
+        <v>0.73499999999999999</v>
+      </c>
+    </row>
+    <row r="1133" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1133" s="27" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D1133" s="27">
+        <v>852614</v>
+      </c>
+      <c r="G1133">
+        <v>0.81899999999999995</v>
+      </c>
+    </row>
+    <row r="1134" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1134" s="27" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D1134" s="27">
+        <v>852615</v>
+      </c>
+      <c r="G1134">
+        <v>0.81699999999999995</v>
+      </c>
+    </row>
+    <row r="1135" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1135" s="27" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D1135" s="27" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G1135">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="1136" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1136" s="27" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D1136" s="27" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G1136">
+        <v>0.68100000000000005</v>
+      </c>
+    </row>
+    <row r="1137" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1137" s="27" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D1137" s="27" t="s">
+        <v>1761</v>
+      </c>
+      <c r="G1137">
+        <v>0.69799999999999995</v>
+      </c>
+    </row>
+    <row r="1138" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1138" s="27" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D1138" s="27" t="s">
+        <v>1762</v>
+      </c>
+      <c r="G1138">
+        <v>0.67300000000000004</v>
+      </c>
+    </row>
+    <row r="1139" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1139" s="27" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D1139" s="27" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G1139">
+        <v>0.627</v>
+      </c>
+    </row>
+    <row r="1140" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1140" s="27" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D1140" s="27" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G1140">
+        <v>0.78700000000000003</v>
+      </c>
+    </row>
+    <row r="1141" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1141" s="27" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D1141" s="27" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G1141">
+        <v>0.69399999999999995</v>
+      </c>
+    </row>
+    <row r="1142" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1142" s="27" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D1142" s="27" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G1142">
+        <v>0.754</v>
+      </c>
+    </row>
+    <row r="1143" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1143" s="27" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D1143" s="27" t="s">
+        <v>1767</v>
+      </c>
+      <c r="G1143">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="1144" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1144" s="27" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1144" s="27">
+        <v>850418</v>
+      </c>
+      <c r="G1144">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1145" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1145" s="27" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1145" s="27">
+        <v>850429</v>
+      </c>
+      <c r="G1145">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1146" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1146" s="27" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D1146" s="27">
+        <v>850438</v>
+      </c>
+      <c r="G1146">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1147" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1147" s="27" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D1147" s="27">
+        <v>850448</v>
+      </c>
+      <c r="G1147">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1148" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1148" s="27" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D1148" s="27">
+        <v>850451</v>
+      </c>
+      <c r="G1148">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1149" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1149" s="27" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1149" s="27">
+        <v>850459</v>
+      </c>
+      <c r="G1149">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1150" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1150" s="27" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D1150" s="27" t="s">
+        <v>1785</v>
+      </c>
+      <c r="G1150">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1151" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1151" s="27" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D1151" s="27" t="s">
+        <v>1786</v>
+      </c>
+      <c r="G1151">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1152" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1152" s="27" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D1152" s="27" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1152">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1153" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1153" s="27" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1153" s="27" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1153">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1154" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1154" s="27" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D1154" s="27" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G1154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1155" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1155" s="27" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D1155" s="27" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G1155">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1156" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1156" s="27" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D1156" s="27" t="s">
+        <v>1791</v>
+      </c>
+      <c r="G1156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1157" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1157" s="27" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1157" s="27" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G1157">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1158" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1158" s="27" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D1158" s="27" t="s">
+        <v>1793</v>
+      </c>
+      <c r="G1158">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1159" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1159" s="27" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D1159" s="27" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1159">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="1160" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1160" s="27" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D1160" s="27" t="s">
+        <v>1795</v>
+      </c>
+      <c r="G1160">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="1161" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1161" s="27" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D1161" s="27" t="s">
+        <v>1796</v>
+      </c>
+      <c r="G1161">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1162" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1162" s="27" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D1162" s="27" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G1162">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="1163" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1163" s="27" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D1163" s="27" t="s">
+        <v>1798</v>
+      </c>
+      <c r="G1163">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1164" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1164" s="27" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D1164" s="27" t="s">
+        <v>1799</v>
+      </c>
+      <c r="G1164">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1165" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1165" s="27" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1165" s="27" t="s">
+        <v>1800</v>
+      </c>
+      <c r="G1165">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1166" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1166" s="27" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1166" s="27" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1166">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1167" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1167" s="27" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D1167" s="27" t="s">
+        <v>1802</v>
+      </c>
+      <c r="G1167">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1168" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1168" s="27" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1168" s="27" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G1168">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1169" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1169" s="27" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D1169" s="27" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G1169">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1170" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1170" s="27" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D1170" s="27" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G1170">
+        <v>0.85</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1067">
+  <conditionalFormatting sqref="D1:D1049">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(D1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="D1050" r:id="rId1" display="https://poolzone-1.admin.s10.upgates.com/manager/products/default/view/35800/" xr:uid="{9203138D-D01D-40C8-BA3D-21B1467F355E}"/>
+    <hyperlink ref="D1051" r:id="rId2" display="https://poolzone-1.admin.s10.upgates.com/manager/products/default/view/35801/" xr:uid="{222D6B97-4EE1-4083-B5B7-721DEB010C87}"/>
+    <hyperlink ref="D1052" r:id="rId3" display="https://poolzone-1.admin.s10.upgates.com/manager/products/default/view/35802/" xr:uid="{6F3AB100-B86C-4A7E-8571-280F67D12A8E}"/>
+    <hyperlink ref="D1053" r:id="rId4" display="https://poolzone-1.admin.s10.upgates.com/manager/products/default/view/35803/" xr:uid="{E76024FA-D10B-4204-8F06-0AF24363F968}"/>
+    <hyperlink ref="D1054" r:id="rId5" display="https://poolzone-1.admin.s10.upgates.com/manager/products/default/view/35804/" xr:uid="{21D7EE18-420E-4109-9046-2D7EED2EF4EF}"/>
+    <hyperlink ref="D1055" r:id="rId6" display="https://poolzone-1.admin.s10.upgates.com/manager/products/default/view/35805/" xr:uid="{7C79830C-DDDE-44F8-8A4B-DF3342D77255}"/>
+    <hyperlink ref="D1056" r:id="rId7" display="https://poolzone-1.admin.s10.upgates.com/manager/products/default/view/35806/" xr:uid="{4C7BE30A-1D77-49D5-A608-C45842698980}"/>
+    <hyperlink ref="D1057" r:id="rId8" display="https://poolzone-1.admin.s10.upgates.com/manager/products/default/view/35807/" xr:uid="{9B1FCDD2-B0E1-4813-9D7F-BE85BCEA2F2B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>